--- a/sample-format/usersPost.xlsx
+++ b/sample-format/usersPost.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mithilesh Thakur\Desktop\import-format\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\gitHub_source_code\excel_to_Json_Converter_angularJS\sample-format\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0571466-7020-4ABC-98DA-B479E741ABC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA9770C8-D0B4-40EF-977D-C515DB9A5EA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1156,9 +1156,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1196,7 +1196,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1302,7 +1302,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1444,7 +1444,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/sample-format/usersPost.xlsx
+++ b/sample-format/usersPost.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\gitHub_source_code\excel_to_Json_Converter_angularJS\sample-format\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA9770C8-D0B4-40EF-977D-C515DB9A5EA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1C6498A-1452-4320-BA6D-942C51F46D1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1452,7 +1452,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:L142"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
@@ -1509,7 +1508,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:12" hidden="1">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1541,7 +1540,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="3" spans="1:12" hidden="1">
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1573,7 +1572,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:12" hidden="1">
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1605,7 +1604,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="5" spans="1:12" hidden="1">
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -1637,7 +1636,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="1:12" hidden="1">
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1669,7 +1668,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:12" hidden="1">
+    <row r="7" spans="1:12">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -1701,7 +1700,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="8" spans="1:12" hidden="1">
+    <row r="8" spans="1:12">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -1759,7 +1758,7 @@
       <c r="K9" s="14"/>
       <c r="L9" s="14"/>
     </row>
-    <row r="10" spans="1:12" hidden="1">
+    <row r="10" spans="1:12">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -1791,7 +1790,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="11" spans="1:12" hidden="1">
+    <row r="11" spans="1:12">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -1823,7 +1822,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="12" spans="1:12" hidden="1">
+    <row r="12" spans="1:12">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -1855,7 +1854,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="13" spans="1:12" hidden="1">
+    <row r="13" spans="1:12">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -1887,7 +1886,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="14" spans="1:12" hidden="1">
+    <row r="14" spans="1:12">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -1919,7 +1918,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="15" spans="1:12" hidden="1">
+    <row r="15" spans="1:12">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -1977,7 +1976,7 @@
       <c r="K16" s="13"/>
       <c r="L16" s="13"/>
     </row>
-    <row r="17" spans="1:12" hidden="1">
+    <row r="17" spans="1:12">
       <c r="A17" t="s">
         <v>27</v>
       </c>
@@ -2035,7 +2034,7 @@
       <c r="K18" s="11"/>
       <c r="L18" s="11"/>
     </row>
-    <row r="19" spans="1:12" hidden="1">
+    <row r="19" spans="1:12">
       <c r="A19" t="s">
         <v>29</v>
       </c>
@@ -2093,7 +2092,7 @@
       <c r="K20" s="11"/>
       <c r="L20" s="11"/>
     </row>
-    <row r="21" spans="1:12" hidden="1">
+    <row r="21" spans="1:12">
       <c r="A21" t="s">
         <v>31</v>
       </c>
@@ -2151,7 +2150,7 @@
       <c r="K22" s="11"/>
       <c r="L22" s="11"/>
     </row>
-    <row r="23" spans="1:12" hidden="1">
+    <row r="23" spans="1:12">
       <c r="A23" t="s">
         <v>33</v>
       </c>
@@ -2183,7 +2182,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="24" spans="1:12" hidden="1">
+    <row r="24" spans="1:12">
       <c r="A24" t="s">
         <v>34</v>
       </c>
@@ -2215,7 +2214,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="1:12" hidden="1">
+    <row r="25" spans="1:12">
       <c r="A25" t="s">
         <v>35</v>
       </c>
@@ -2247,7 +2246,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="26" spans="1:12" hidden="1">
+    <row r="26" spans="1:12">
       <c r="A26" t="s">
         <v>36</v>
       </c>
@@ -2279,7 +2278,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="27" spans="1:12" hidden="1">
+    <row r="27" spans="1:12">
       <c r="A27" t="s">
         <v>37</v>
       </c>
@@ -2311,7 +2310,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="28" spans="1:12" hidden="1">
+    <row r="28" spans="1:12">
       <c r="A28" t="s">
         <v>38</v>
       </c>
@@ -2343,7 +2342,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="29" spans="1:12" hidden="1">
+    <row r="29" spans="1:12">
       <c r="A29" t="s">
         <v>39</v>
       </c>
@@ -2375,7 +2374,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="30" spans="1:12" hidden="1">
+    <row r="30" spans="1:12">
       <c r="A30" t="s">
         <v>40</v>
       </c>
@@ -2407,7 +2406,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="31" spans="1:12" hidden="1">
+    <row r="31" spans="1:12">
       <c r="A31" t="s">
         <v>41</v>
       </c>
@@ -2439,7 +2438,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="32" spans="1:12" hidden="1">
+    <row r="32" spans="1:12">
       <c r="A32" t="s">
         <v>42</v>
       </c>
@@ -2471,7 +2470,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="33" spans="1:12" hidden="1">
+    <row r="33" spans="1:12">
       <c r="A33" s="15" t="s">
         <v>146</v>
       </c>
@@ -2529,7 +2528,7 @@
       <c r="K34" s="11"/>
       <c r="L34" s="11"/>
     </row>
-    <row r="35" spans="1:12" hidden="1">
+    <row r="35" spans="1:12">
       <c r="A35" s="15" t="s">
         <v>148</v>
       </c>
@@ -2561,7 +2560,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="36" spans="1:12" hidden="1">
+    <row r="36" spans="1:12">
       <c r="A36" s="15" t="s">
         <v>149</v>
       </c>
@@ -3126,11 +3125,6 @@
       <c r="J142"/>
     </row>
   </sheetData>
-  <autoFilter ref="J1:J142" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters blank="1"/>
-    </filterColumn>
-  </autoFilter>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="B2:B36">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
